--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run4/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run4/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="494">
   <si>
     <t>Filename</t>
   </si>
@@ -808,16 +808,25 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9505,0.0006,0.0241,0.0055</t>
-  </si>
-  <si>
-    <t>0.0013,0.0001,0.0006,0.9993</t>
-  </si>
-  <si>
-    <t>0.9642,0.0000,0.0005,0.0428</t>
-  </si>
-  <si>
-    <t>0.0427,0.0001,0.0002,0.9912</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.8847,0.0043,0.0494,0.0170</t>
+  </si>
+  <si>
+    <t>0.0030,0.0001,0.0002,0.9991</t>
+  </si>
+  <si>
+    <t>0.9929,0.0000,0.0001,0.0069</t>
+  </si>
+  <si>
+    <t>0.2340,0.0000,0.0000,0.9424</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
@@ -826,652 +835,667 @@
     <t>0.9999,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0011,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9945,0.0005,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.4027,0.0005,0.7250,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.0020,0.9951,0.0006</t>
+  </si>
+  <si>
+    <t>0.9941,0.0010,0.0019,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0034,0.9958,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.8735,0.0010,0.1266,0.0005</t>
+  </si>
+  <si>
+    <t>0.0219,0.0088,0.9717,0.0012</t>
+  </si>
+  <si>
+    <t>0.0060,0.0008,0.9943,0.0002</t>
+  </si>
+  <si>
+    <t>0.0020,0.0018,0.9958,0.0004</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0650,0.9287,0.0040,0.0007</t>
+  </si>
+  <si>
+    <t>0.9690,0.0136,0.0043,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0004</t>
+  </si>
+  <si>
+    <t>0.0028,0.9880,0.0107,0.0000</t>
+  </si>
+  <si>
+    <t>0.9062,0.0003,0.0667,0.0016</t>
+  </si>
+  <si>
+    <t>0.9862,0.0029,0.0031,0.0001</t>
+  </si>
+  <si>
+    <t>0.1381,0.8291,0.0107,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.9966,0.0049,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.6065,0.6951,0.0004</t>
+  </si>
+  <si>
+    <t>0.0043,0.0019,0.9905,0.0011</t>
+  </si>
+  <si>
+    <t>0.0063,0.0863,0.9656,0.0013</t>
+  </si>
+  <si>
+    <t>0.0097,0.0003,0.9919,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.0018,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.6356,0.0000,0.6415</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0040,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0111,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0747,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.0003,0.9971,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9993,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0018,0.0027,0.9945,0.0018</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0004,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9936,0.0057,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9950,0.9967,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0007,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0062,0.9982,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9892,0.9610,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0070,0.9945,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9997,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9437,0.0001,0.1060,0.0001</t>
+  </si>
+  <si>
+    <t>0.9871,0.0011,0.0091,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.9967,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9936,0.0673,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9935,0.9836,0.0000</t>
+  </si>
+  <si>
+    <t>0.0092,0.0003,0.0044,0.9919</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0010,0.0014,0.0002,0.9994</t>
+  </si>
+  <si>
+    <t>0.0040,0.0002,0.0009,0.9979</t>
+  </si>
+  <si>
+    <t>0.0034,0.0000,0.0005,0.9984</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0003,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.9988,0.6201,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0714,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.0759,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9791,0.7417,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9926,0.9852,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9961,0.0033,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9978,0.0037,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0007,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9994,0.0005,0.0000,0.0000</t>
+    <t>0.0015,0.0000,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0003,0.9986,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0001,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9992,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9976,0.0027,0.0012</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.2173,0.8201,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.9618,0.0015,0.0364,0.0004</t>
+  </si>
+  <si>
+    <t>0.0341,0.0005,0.9782,0.0004</t>
+  </si>
+  <si>
+    <t>0.2240,0.0465,0.6075,0.0044</t>
+  </si>
+  <si>
+    <t>0.1543,0.0133,0.7716,0.0014</t>
+  </si>
+  <si>
+    <t>0.0010,0.0418,0.0014,0.9951</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9964,0.8619,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9996,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.1768,0.8705,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.4658,0.5606,0.0043,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.6163,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.1553,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0058,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0036,0.9982,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9576,0.0020,0.0284,0.0025</t>
+  </si>
+  <si>
+    <t>0.0280,0.0003,0.9787,0.0009</t>
+  </si>
+  <si>
+    <t>0.7618,0.0449,0.0732,0.0039</t>
+  </si>
+  <si>
+    <t>0.1031,0.0000,0.0001,0.9726</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0015,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0002,0.9827,0.9161,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0034,0.9943,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.6297,0.4328,0.0027,0.0000</t>
+  </si>
+  <si>
+    <t>0.0510,0.0000,0.0001,0.9939</t>
+  </si>
+  <si>
+    <t>0.0006,0.0031,0.9991,0.0003</t>
+  </si>
+  <si>
+    <t>0.9980,0.0000,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9984,0.0001,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.3627,0.6707,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9942,0.0009,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.9979,0.0005,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.3847,0.6406,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9968,0.0004,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.9845,0.0047,0.0049,0.0004</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.8226,0.2393,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.7072,0.3509,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.6900,0.4125,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.8860,0.0241,0.0692,0.0002</t>
+  </si>
+  <si>
+    <t>0.9973,0.0026,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9949,0.0037,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0008,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9868,0.0059,0.0022,0.0014</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9910,0.0031,0.0029,0.0005</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0207,0.9954,0.0008</t>
+  </si>
+  <si>
+    <t>0.0012,0.0002,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.3366,0.0132,0.4275,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0012,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0035,0.0051,0.9938,0.0004</t>
+  </si>
+  <si>
+    <t>0.0028,0.0009,0.9966,0.0002</t>
+  </si>
+  <si>
+    <t>0.8701,0.0061,0.0641,0.0088</t>
+  </si>
+  <si>
+    <t>0.3930,0.0285,0.3862,0.0005</t>
+  </si>
+  <si>
+    <t>0.0482,0.3377,0.2632,0.0004</t>
+  </si>
+  <si>
+    <t>0.7731,0.0013,0.2234,0.0000</t>
+  </si>
+  <si>
+    <t>0.9713,0.0007,0.0280,0.0005</t>
+  </si>
+  <si>
+    <t>0.8437,0.0158,0.1032,0.0021</t>
+  </si>
+  <si>
+    <t>0.0229,0.9782,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.1160,0.9115,0.0043,0.0000</t>
+  </si>
+  <si>
+    <t>0.2678,0.8291,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.8377,0.2025,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0940,0.9447,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.6301,0.2363,0.0051,0.0007</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9945,0.0004,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.0794,0.0835,0.6646,0.0034</t>
+  </si>
+  <si>
+    <t>0.9947,0.0002,0.0042,0.0000</t>
+  </si>
+  <si>
+    <t>0.0143,0.0010,0.9876,0.0022</t>
+  </si>
+  <si>
+    <t>0.0013,0.0179,0.9896,0.0003</t>
+  </si>
+  <si>
+    <t>0.0174,0.0179,0.9637,0.0005</t>
+  </si>
+  <si>
+    <t>0.3130,0.0002,0.7328,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.0113,0.9952,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0018,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9914,0.0080,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9924,0.0073,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9975,0.0013,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.9998,0.0018</t>
+  </si>
+  <si>
+    <t>0.0111,0.0219,0.9733,0.0041</t>
+  </si>
+  <si>
+    <t>0.0826,0.0007,0.9440,0.0009</t>
+  </si>
+  <si>
+    <t>0.0012,0.0036,0.9975,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.0003,0.9978,0.0001</t>
+  </si>
+  <si>
+    <t>0.0110,0.0007,0.9906,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0050,0.9992,0.0005</t>
+  </si>
+  <si>
+    <t>0.9867,0.0002,0.0149,0.0000</t>
+  </si>
+  <si>
+    <t>0.1254,0.0004,0.9169,0.0003</t>
+  </si>
+  <si>
+    <t>0.9972,0.0007,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9978,0.0010,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0010,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9990,0.0009,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9971,0.0005,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0043,0.0061,0.9948,0.0004</t>
-  </si>
-  <si>
-    <t>0.2167,0.0009,0.8307,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0019,0.9989,0.0002</t>
-  </si>
-  <si>
-    <t>0.8534,0.0010,0.1650,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9984,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9995,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.3859,0.0005,0.6664,0.0008</t>
-  </si>
-  <si>
-    <t>0.7773,0.0024,0.2335,0.0006</t>
-  </si>
-  <si>
-    <t>0.0056,0.0027,0.9962,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0019,0.9973,0.0005</t>
-  </si>
-  <si>
-    <t>0.0017,0.0004,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0001</t>
+    <t>0.0034,0.0125,0.9882,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0010,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0054,0.9979,0.0001</t>
+  </si>
+  <si>
+    <t>0.0094,0.1482,0.8398,0.0043</t>
   </si>
   <si>
     <t>0.0001,0.0002,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.9970,0.0013,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9547,0.0271,0.0055,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.0115,0.9795,0.0043,0.0000</t>
-  </si>
-  <si>
-    <t>0.8174,0.0008,0.1646,0.0007</t>
-  </si>
-  <si>
-    <t>0.9933,0.0007,0.0021,0.0000</t>
-  </si>
-  <si>
-    <t>0.1739,0.8723,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0034,0.0000</t>
-  </si>
-  <si>
-    <t>0.0056,0.1909,0.8540,0.0001</t>
-  </si>
-  <si>
-    <t>0.0471,0.0053,0.9248,0.0033</t>
-  </si>
-  <si>
-    <t>0.0087,0.0089,0.9836,0.0008</t>
-  </si>
-  <si>
-    <t>0.0138,0.0007,0.9844,0.0008</t>
-  </si>
-  <si>
-    <t>0.0021,0.0063,0.9968,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0028,0.9980,0.0013</t>
-  </si>
-  <si>
-    <t>0.0192,0.0244,0.0000,0.8705</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0034,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.1456,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0004,0.9984,0.0004</t>
-  </si>
-  <si>
-    <t>0.0011,0.0002,0.9987,0.0003</t>
-  </si>
-  <si>
-    <t>0.0010,0.0003,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9990,0.0008</t>
-  </si>
-  <si>
-    <t>0.9893,0.0192,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0005,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0005,0.9994,0.0003</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9967,0.0034,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9982,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0056,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0045,0.9984,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9851,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.9986,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.4505,0.0015,0.6828,0.0006</t>
-  </si>
-  <si>
-    <t>0.0490,0.0036,0.9595,0.0016</t>
-  </si>
-  <si>
-    <t>0.0025,0.0006,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.8803,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9359,0.9538,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9923,0.9535,0.0000</t>
-  </si>
-  <si>
-    <t>0.0390,0.0002,0.0692,0.8656</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0002,0.9999</t>
-  </si>
-  <si>
-    <t>0.0147,0.0008,0.0021,0.9921</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.0014,0.9990</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0005,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9989,0.8213,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.3631,0.9971,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0030,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9762,0.9532,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.9955,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9903,0.9976,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9952,0.0055,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0011,0.9981,0.0004</t>
-  </si>
-  <si>
-    <t>0.9965,0.0001,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0680,0.9316,0.0046,0.0005</t>
-  </si>
-  <si>
-    <t>0.9770,0.0018,0.0108,0.0019</t>
-  </si>
-  <si>
-    <t>0.7135,0.0003,0.3717,0.0001</t>
-  </si>
-  <si>
-    <t>0.9197,0.0241,0.0151,0.0002</t>
-  </si>
-  <si>
-    <t>0.4293,0.0076,0.4754,0.0012</t>
-  </si>
-  <si>
-    <t>0.0014,0.0178,0.0028,0.9958</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0026,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.9458,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.7209,0.3223,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.8291,0.1827,0.0024,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.7286,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.2984,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0030,0.0185,0.9950,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0018,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.9971,0.0001,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9793,0.0012,0.0161,0.0005</t>
-  </si>
-  <si>
-    <t>0.0487,0.0004,0.9679,0.0006</t>
-  </si>
-  <si>
-    <t>0.8210,0.0324,0.0722,0.0020</t>
-  </si>
-  <si>
-    <t>0.1384,0.0001,0.0001,0.9456</t>
+    <t>0.2043,0.0013,0.7500,0.0238</t>
+  </si>
+  <si>
+    <t>0.1178,0.0004,0.8947,0.0015</t>
+  </si>
+  <si>
+    <t>0.0033,0.0004,0.9930,0.0012</t>
+  </si>
+  <si>
+    <t>0.7078,0.0000,0.0009,0.5606</t>
+  </si>
+  <si>
+    <t>0.0013,0.0118,0.0005,0.9984</t>
+  </si>
+  <si>
+    <t>0.0012,0.0000,0.0002,0.9996</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.0000,0.9999</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0007,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.9984,0.1029,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0022,0.9952,0.0010,0.0019</t>
-  </si>
-  <si>
-    <t>0.9986,0.0002,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.2184,0.8487,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.1491,0.0000,0.0001,0.9745</t>
-  </si>
-  <si>
-    <t>0.0003,0.0736,0.9984,0.0004</t>
-  </si>
-  <si>
-    <t>0.9862,0.0000,0.0014,0.0080</t>
-  </si>
-  <si>
-    <t>0.9828,0.0002,0.0087,0.0047</t>
-  </si>
-  <si>
-    <t>0.0614,0.9454,0.0018,0.0002</t>
-  </si>
-  <si>
-    <t>0.9984,0.0001,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0004,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.5555,0.4087,0.0019,0.0008</t>
-  </si>
-  <si>
-    <t>0.9951,0.0013,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.9855,0.0059,0.0030,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.7459,0.3252,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.5056,0.5653,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.2312,0.8446,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.0480,0.0360,0.9563,0.0014</t>
-  </si>
-  <si>
-    <t>0.9948,0.0056,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0008,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9537,0.0487,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9809,0.0060,0.0083,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.0013,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0494,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0306,0.0068,0.9367,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0249,0.0078,0.9626,0.0019</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0171,0.0049,0.9775,0.0035</t>
-  </si>
-  <si>
-    <t>0.0082,0.0192,0.9671,0.0008</t>
-  </si>
-  <si>
-    <t>0.2625,0.0293,0.5050,0.0003</t>
-  </si>
-  <si>
-    <t>0.8927,0.0070,0.0600,0.0001</t>
-  </si>
-  <si>
-    <t>0.9889,0.0003,0.0071,0.0004</t>
-  </si>
-  <si>
-    <t>0.1569,0.0053,0.8474,0.0011</t>
-  </si>
-  <si>
-    <t>0.0121,0.9880,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0081,0.9932,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.3185,0.8300,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.2048,0.8662,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0303,0.9704,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.7412,0.1528,0.0054,0.0012</t>
-  </si>
-  <si>
-    <t>0.9978,0.0003,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9921,0.0012,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9141,0.0263,0.0111,0.0006</t>
-  </si>
-  <si>
-    <t>0.9957,0.0000,0.0046,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.0005,0.9974,0.0013</t>
-  </si>
-  <si>
-    <t>0.0008,0.0643,0.9827,0.0002</t>
-  </si>
-  <si>
-    <t>0.0016,0.0734,0.9927,0.0004</t>
-  </si>
-  <si>
-    <t>0.7980,0.0019,0.1599,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0060,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.9973,0.0011,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0012,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9953,0.0024,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0004,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0009,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0081,0.7058,0.5154,0.0007</t>
-  </si>
-  <si>
-    <t>0.1428,0.0011,0.9021,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0007,0.9992,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.0070,0.9967,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.0006,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0010,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0066,0.9979,0.0008</t>
-  </si>
-  <si>
-    <t>0.9658,0.0008,0.0340,0.0004</t>
-  </si>
-  <si>
-    <t>0.9970,0.0001,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9960,0.0019,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0010,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0270,0.0096,0.9456,0.0001</t>
-  </si>
-  <si>
-    <t>0.0048,0.0291,0.9645,0.0001</t>
-  </si>
-  <si>
-    <t>0.0120,0.1693,0.6563,0.0014</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.6294,0.0023,0.3507,0.0043</t>
-  </si>
-  <si>
-    <t>0.0036,0.0021,0.9910,0.0021</t>
-  </si>
-  <si>
-    <t>0.4105,0.0011,0.5508,0.0006</t>
-  </si>
-  <si>
-    <t>0.9335,0.0000,0.0013,0.1251</t>
-  </si>
-  <si>
-    <t>0.0010,0.0531,0.0008,0.9979</t>
-  </si>
-  <si>
-    <t>0.0023,0.0000,0.0013,0.9987</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9013,0.0002,0.0029,0.0953</t>
+    <t>0.7544,0.0019,0.0002,0.2837</t>
   </si>
 </sst>
 </file>
@@ -1857,7 +1881,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1871,7 +1895,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1885,7 +1909,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1899,7 +1923,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1913,7 +1937,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1927,7 +1951,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1941,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1969,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1983,7 +2007,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1997,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2025,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2039,7 +2063,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2053,7 +2077,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2067,7 +2091,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2081,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2095,7 +2119,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2109,7 +2133,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2123,7 +2147,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2137,7 +2161,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2151,7 +2175,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2162,10 +2186,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2176,10 +2200,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2193,7 +2217,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2207,7 +2231,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2221,7 +2245,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2235,7 +2259,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2249,7 +2273,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2260,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2277,7 +2301,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2291,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2305,7 +2329,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2319,7 +2343,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2333,7 +2357,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2347,7 +2371,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2361,7 +2385,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2372,10 +2396,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2389,7 +2413,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2403,7 +2427,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2417,7 +2441,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2431,7 +2455,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2445,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2459,7 +2483,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2470,10 +2494,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2487,7 +2511,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2501,7 +2525,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2515,7 +2539,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2529,7 +2553,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2543,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2557,7 +2581,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2571,7 +2595,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2585,7 +2609,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2599,7 +2623,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2613,7 +2637,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2627,7 +2651,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2641,7 +2665,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2655,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2669,7 +2693,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2683,7 +2707,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>269</v>
+        <v>323</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2697,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2711,7 +2735,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2725,7 +2749,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2739,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2753,7 +2777,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2767,7 +2791,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2781,7 +2805,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2795,7 +2819,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2806,10 +2830,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2820,10 +2844,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2837,7 +2861,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2851,7 +2875,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2862,10 +2886,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2879,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2893,7 +2917,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2907,7 +2931,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2921,7 +2945,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2935,7 +2959,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2949,7 +2973,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2963,7 +2987,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2977,7 +3001,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2991,7 +3015,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3005,7 +3029,7 @@
         <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3019,7 +3043,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3033,7 +3057,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3047,7 +3071,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3061,7 +3085,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3075,7 +3099,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3089,7 +3113,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>272</v>
+        <v>352</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3103,7 +3127,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3117,7 +3141,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>320</v>
+        <v>354</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3131,7 +3155,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3145,7 +3169,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3159,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3173,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3187,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3201,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3215,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3229,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3243,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3257,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>353</v>
+        <v>323</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3271,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>268</v>
+        <v>358</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3285,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3299,7 +3323,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3313,7 +3337,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3327,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3341,7 +3365,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3355,7 +3379,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>304</v>
+        <v>363</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3369,7 +3393,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3383,7 +3407,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3397,7 +3421,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3411,7 +3435,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>361</v>
+        <v>306</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3425,7 +3449,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3439,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3453,7 +3477,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3464,10 +3488,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3478,10 +3502,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3492,10 +3516,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3509,7 +3533,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3523,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3537,7 +3561,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>361</v>
+        <v>306</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3551,7 +3575,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3565,7 +3589,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3579,7 +3603,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3590,10 +3614,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3604,10 +3628,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3621,7 +3645,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>271</v>
+        <v>380</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3635,7 +3659,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>320</v>
+        <v>381</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3649,7 +3673,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>271</v>
+        <v>382</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3663,7 +3687,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3677,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3691,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3705,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>320</v>
+        <v>386</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3719,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>271</v>
+        <v>387</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3733,7 +3757,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3747,7 +3771,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3761,7 +3785,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3775,7 +3799,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3789,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3803,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3817,7 +3841,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3831,7 +3855,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3845,7 +3869,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3859,7 +3883,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3873,7 +3897,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3887,7 +3911,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3898,10 +3922,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3915,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3929,7 +3953,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3943,7 +3967,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3954,10 +3978,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3971,7 +3995,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3985,7 +4009,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3999,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4013,7 +4037,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4027,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4041,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4055,7 +4079,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4069,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4083,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4094,10 +4118,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4111,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4125,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4139,7 +4163,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4153,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4167,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4181,7 +4205,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4195,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4209,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>410</v>
+        <v>380</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4237,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>271</v>
+        <v>358</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4251,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4262,10 +4286,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4276,10 +4300,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4290,10 +4314,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4307,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4321,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4335,7 +4359,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4349,7 +4373,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4363,7 +4387,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4377,7 +4401,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4391,7 +4415,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4405,7 +4429,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4419,7 +4443,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4430,10 +4454,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D186" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4447,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4461,7 +4485,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4475,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>354</v>
+        <v>435</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4489,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4503,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4514,10 +4538,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4528,10 +4552,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D193" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4542,10 +4566,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D194" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4559,7 +4583,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4573,7 +4597,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4584,10 +4608,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4601,7 +4625,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4615,7 +4639,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4629,7 +4653,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4640,10 +4664,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4657,7 +4681,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4671,7 +4695,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4685,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4699,7 +4723,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4710,10 +4734,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4727,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4741,7 +4765,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4755,7 +4779,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4769,7 +4793,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4780,10 +4804,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4797,7 +4821,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4811,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>377</v>
+        <v>271</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4825,7 +4849,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4839,7 +4863,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4853,7 +4877,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>406</v>
+        <v>461</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4867,7 +4891,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4881,7 +4905,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4895,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>454</v>
+        <v>385</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4909,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>408</v>
+        <v>464</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4923,7 +4947,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4934,10 +4958,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4951,7 +4975,7 @@
         <v>261</v>
       </c>
       <c r="D223" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4965,7 +4989,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>458</v>
+        <v>292</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4979,7 +5003,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>459</v>
+        <v>362</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4993,7 +5017,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5007,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5021,7 +5045,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5035,7 +5059,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5049,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5063,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5077,7 +5101,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5088,10 +5112,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5105,7 +5129,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5119,7 +5143,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>468</v>
+        <v>272</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5133,7 +5157,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5147,7 +5171,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5161,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5189,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5203,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5217,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>473</v>
+        <v>351</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5231,7 +5255,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5245,7 +5269,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>425</v>
+        <v>481</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5259,7 +5283,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5273,7 +5297,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5287,7 +5311,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5298,10 +5322,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5315,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5329,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5340,10 +5364,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D251" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5357,7 +5381,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5371,7 +5395,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5385,7 +5409,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5399,7 +5423,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>387</v>
+        <v>492</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5413,7 +5437,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
